--- a/artfynd/A 7520-2026 artfynd.xlsx
+++ b/artfynd/A 7520-2026 artfynd.xlsx
@@ -787,42 +787,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131663953</v>
+        <v>131661542</v>
       </c>
       <c r="B3" t="n">
-        <v>99033</v>
+        <v>58057</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589499</v>
+        <v>589543</v>
       </c>
       <c r="R3" t="n">
-        <v>6386932</v>
+        <v>6386905</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,42 +903,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131661542</v>
+        <v>131663953</v>
       </c>
       <c r="B4" t="n">
-        <v>58057</v>
+        <v>99033</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -947,13 +947,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589543</v>
+        <v>589499</v>
       </c>
       <c r="R4" t="n">
-        <v>6386905</v>
+        <v>6386932</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,32 +1019,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131662181</v>
+        <v>131662120</v>
       </c>
       <c r="B5" t="n">
-        <v>57892</v>
+        <v>99033</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102977</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1054,13 +1054,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589510</v>
+        <v>589504</v>
       </c>
       <c r="R5" t="n">
-        <v>6386923</v>
+        <v>6386928</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,32 +1126,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131662120</v>
+        <v>131662181</v>
       </c>
       <c r="B6" t="n">
-        <v>99033</v>
+        <v>57892</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>102977</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1161,13 +1161,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589504</v>
+        <v>589510</v>
       </c>
       <c r="R6" t="n">
-        <v>6386928</v>
+        <v>6386923</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 7520-2026 artfynd.xlsx
+++ b/artfynd/A 7520-2026 artfynd.xlsx
@@ -787,42 +787,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131661542</v>
+        <v>131663953</v>
       </c>
       <c r="B3" t="n">
-        <v>58057</v>
+        <v>99033</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589543</v>
+        <v>589499</v>
       </c>
       <c r="R3" t="n">
-        <v>6386905</v>
+        <v>6386932</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,42 +903,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131663953</v>
+        <v>131661542</v>
       </c>
       <c r="B4" t="n">
-        <v>99033</v>
+        <v>58057</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -947,13 +947,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589499</v>
+        <v>589543</v>
       </c>
       <c r="R4" t="n">
-        <v>6386932</v>
+        <v>6386905</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 7520-2026 artfynd.xlsx
+++ b/artfynd/A 7520-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>131663953</v>
       </c>
       <c r="B3" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1019,32 +1019,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131662120</v>
+        <v>131662181</v>
       </c>
       <c r="B5" t="n">
-        <v>99033</v>
+        <v>57892</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>102977</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1054,13 +1054,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589504</v>
+        <v>589510</v>
       </c>
       <c r="R5" t="n">
-        <v>6386928</v>
+        <v>6386923</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,32 +1126,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131662181</v>
+        <v>131662120</v>
       </c>
       <c r="B6" t="n">
-        <v>57892</v>
+        <v>99034</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102977</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1161,13 +1161,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589510</v>
+        <v>589504</v>
       </c>
       <c r="R6" t="n">
-        <v>6386923</v>
+        <v>6386928</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1459,7 +1459,7 @@
         <v>131662287</v>
       </c>
       <c r="B9" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>131661395</v>
       </c>
       <c r="B10" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>131662531</v>
       </c>
       <c r="B11" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 7520-2026 artfynd.xlsx
+++ b/artfynd/A 7520-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131662872</v>
       </c>
       <c r="B2" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,42 +787,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131663953</v>
+        <v>131661542</v>
       </c>
       <c r="B3" t="n">
-        <v>99034</v>
+        <v>58058</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589499</v>
+        <v>589543</v>
       </c>
       <c r="R3" t="n">
-        <v>6386932</v>
+        <v>6386905</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,42 +903,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131661542</v>
+        <v>131663953</v>
       </c>
       <c r="B4" t="n">
-        <v>58057</v>
+        <v>99035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -947,13 +947,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589543</v>
+        <v>589499</v>
       </c>
       <c r="R4" t="n">
-        <v>6386905</v>
+        <v>6386932</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,7 +1022,7 @@
         <v>131662181</v>
       </c>
       <c r="B5" t="n">
-        <v>57892</v>
+        <v>57893</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>131662120</v>
       </c>
       <c r="B6" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>131662253</v>
       </c>
       <c r="B7" t="n">
-        <v>58579</v>
+        <v>58580</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>131663337</v>
       </c>
       <c r="B8" t="n">
-        <v>58057</v>
+        <v>58058</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>131662287</v>
       </c>
       <c r="B9" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>131661395</v>
       </c>
       <c r="B10" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>131662531</v>
       </c>
       <c r="B11" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>131663180</v>
       </c>
       <c r="B12" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 7520-2026 artfynd.xlsx
+++ b/artfynd/A 7520-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131662872</v>
       </c>
       <c r="B2" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>131661542</v>
       </c>
       <c r="B3" t="n">
-        <v>58058</v>
+        <v>58061</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>131663953</v>
       </c>
       <c r="B4" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>131662181</v>
       </c>
       <c r="B5" t="n">
-        <v>57893</v>
+        <v>57896</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>131662120</v>
       </c>
       <c r="B6" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>131662253</v>
       </c>
       <c r="B7" t="n">
-        <v>58580</v>
+        <v>58583</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>131663337</v>
       </c>
       <c r="B8" t="n">
-        <v>58058</v>
+        <v>58061</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>131662287</v>
       </c>
       <c r="B9" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>131661395</v>
       </c>
       <c r="B10" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>131662531</v>
       </c>
       <c r="B11" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>131663180</v>
       </c>
       <c r="B12" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 7520-2026 artfynd.xlsx
+++ b/artfynd/A 7520-2026 artfynd.xlsx
@@ -1019,32 +1019,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131662181</v>
+        <v>131662120</v>
       </c>
       <c r="B5" t="n">
-        <v>57896</v>
+        <v>99038</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102977</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1054,13 +1054,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589510</v>
+        <v>589504</v>
       </c>
       <c r="R5" t="n">
-        <v>6386923</v>
+        <v>6386928</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,32 +1126,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131662120</v>
+        <v>131662181</v>
       </c>
       <c r="B6" t="n">
-        <v>99038</v>
+        <v>57896</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>102977</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1161,13 +1161,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589504</v>
+        <v>589510</v>
       </c>
       <c r="R6" t="n">
-        <v>6386928</v>
+        <v>6386923</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 7520-2026 artfynd.xlsx
+++ b/artfynd/A 7520-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131662872</v>
       </c>
       <c r="B2" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>131661542</v>
       </c>
       <c r="B3" t="n">
-        <v>58061</v>
+        <v>58063</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>131663953</v>
       </c>
       <c r="B4" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,32 +1019,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131662120</v>
+        <v>131662181</v>
       </c>
       <c r="B5" t="n">
-        <v>99038</v>
+        <v>57898</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>102977</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1054,13 +1054,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589504</v>
+        <v>589510</v>
       </c>
       <c r="R5" t="n">
-        <v>6386928</v>
+        <v>6386923</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,32 +1126,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131662181</v>
+        <v>131662120</v>
       </c>
       <c r="B6" t="n">
-        <v>57896</v>
+        <v>99044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102977</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1161,13 +1161,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589510</v>
+        <v>589504</v>
       </c>
       <c r="R6" t="n">
-        <v>6386923</v>
+        <v>6386928</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,7 +1236,7 @@
         <v>131662253</v>
       </c>
       <c r="B7" t="n">
-        <v>58583</v>
+        <v>58585</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>131663337</v>
       </c>
       <c r="B8" t="n">
-        <v>58061</v>
+        <v>58063</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>131662287</v>
       </c>
       <c r="B9" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>131661395</v>
       </c>
       <c r="B10" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>131662531</v>
       </c>
       <c r="B11" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>131663180</v>
       </c>
       <c r="B12" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 7520-2026 artfynd.xlsx
+++ b/artfynd/A 7520-2026 artfynd.xlsx
@@ -787,42 +787,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131661542</v>
+        <v>131663953</v>
       </c>
       <c r="B3" t="n">
-        <v>58063</v>
+        <v>99044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589543</v>
+        <v>589499</v>
       </c>
       <c r="R3" t="n">
-        <v>6386905</v>
+        <v>6386932</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,42 +903,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131663953</v>
+        <v>131661542</v>
       </c>
       <c r="B4" t="n">
-        <v>99044</v>
+        <v>58063</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -947,13 +947,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589499</v>
+        <v>589543</v>
       </c>
       <c r="R4" t="n">
-        <v>6386932</v>
+        <v>6386905</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 7520-2026 artfynd.xlsx
+++ b/artfynd/A 7520-2026 artfynd.xlsx
@@ -787,42 +787,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131663953</v>
+        <v>131661542</v>
       </c>
       <c r="B3" t="n">
-        <v>99044</v>
+        <v>58063</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589499</v>
+        <v>589543</v>
       </c>
       <c r="R3" t="n">
-        <v>6386932</v>
+        <v>6386905</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,42 +903,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131661542</v>
+        <v>131663953</v>
       </c>
       <c r="B4" t="n">
-        <v>58063</v>
+        <v>99044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -947,13 +947,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589543</v>
+        <v>589499</v>
       </c>
       <c r="R4" t="n">
-        <v>6386905</v>
+        <v>6386932</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
